--- a/mixs-templates/Mimag_plus_combinations/MimagFoodHumanFoods.xlsx
+++ b/mixs-templates/Mimag_plus_combinations/MimagFoodHumanFoods.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FB1"/>
+  <dimension ref="A1:FD1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,585 +624,595 @@
       </c>
       <c r="AP1" t="inlineStr">
         <is>
+          <t>marker_gene_recov</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>marker_gene_recov_sw</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
           <t>pos_cont_type</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>feat_pred</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>compl_software</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>env_local_scale</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>samp_mat_process</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>sim_search_meth</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>depth</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>samp_collect_method</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>compl_appr</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>env_medium</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>samp_taxon_id</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>geo_loc_name</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>collection_date</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>seq_meth</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>lat_lon</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>elev</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>env_broad_scale</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>tax_class</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>experimental_factor</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>associated_resource</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>sop</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>organism_count</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>spikein_count</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>samp_store_temp</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>samp_store_dur</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>pool_dna_extracts</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>samp_store_loc</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>genetic_mod</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>perturbation</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>coll_site_geo_feat</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>food_product_type</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>IFSAC_category</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>ferm_chem_add</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>ferm_chem_add_perc</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>ferm_headspace_oxy</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>ferm_medium</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>ferm_pH</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>ferm_rel_humidity</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>ferm_temp</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>ferm_time</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>ferm_vessel</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>bacterial_density</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>cons_food_stor_dur</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>cons_food_stor_temp</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>cons_purch_date</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>cons_qty_purchased</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>cult_isol_date</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>cult_result</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>cult_result_org</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>cult_target</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>dietary_claim_use</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>enrichment_protocol</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>food_additive</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>food_allergen_label</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>food_contact_surf</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>food_contain_wrap</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>food_cooking_proc</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>food_dis_point</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>food_ingredient</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>food_name_status</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>food_origin</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>food_pack_capacity</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>food_pack_integrity</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>food_pack_medium</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>food_preserv_proc</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>food_prior_contact</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>food_prod</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>food_prod_synonym</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>food_product_qual</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>food_quality_date</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>food_source</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>food_trace_list</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>food_trav_mode</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>food_trav_vehic</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>food_treat_proc</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>HACCP_term</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>intended_consumer</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>library_prep_kit</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>lot_number</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>microb_cult_med</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>microb_start</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>microb_start_count</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>microb_start_inoc</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>microb_start_prep</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>microb_start_source</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>microb_start_taxID</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>nucl_acid_ext_kit</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>num_samp_collect</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>part_plant_animal</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>repository_name</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>samp_pooling</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>samp_rep_biol</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>samp_rep_tech</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>samp_source_mat_cat</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>samp_stor_device</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>samp_stor_media</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>samp_transport_cont</t>
         </is>
       </c>
-      <c r="EI1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>samp_transport_dur</t>
         </is>
       </c>
-      <c r="EJ1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>samp_transport_temp</t>
         </is>
       </c>
-      <c r="EK1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>samp_purpose</t>
         </is>
       </c>
-      <c r="EL1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>sequencing_kit</t>
         </is>
       </c>
-      <c r="EM1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>sequencing_location</t>
         </is>
       </c>
-      <c r="EN1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>serovar_or_serotype</t>
         </is>
       </c>
-      <c r="EO1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>spikein_AMR</t>
         </is>
       </c>
-      <c r="EP1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>spikein_antibiotic</t>
         </is>
       </c>
-      <c r="EQ1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>spikein_growth_med</t>
         </is>
       </c>
-      <c r="ER1" t="inlineStr">
+      <c r="ET1" t="inlineStr">
         <is>
           <t>spikein_metal</t>
         </is>
       </c>
-      <c r="ES1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>spikein_org</t>
         </is>
       </c>
-      <c r="ET1" t="inlineStr">
+      <c r="EV1" t="inlineStr">
         <is>
           <t>spikein_serovar</t>
         </is>
       </c>
-      <c r="EU1" t="inlineStr">
+      <c r="EW1" t="inlineStr">
         <is>
           <t>spikein_strain</t>
         </is>
       </c>
-      <c r="EV1" t="inlineStr">
+      <c r="EX1" t="inlineStr">
         <is>
           <t>study_design</t>
         </is>
       </c>
-      <c r="EW1" t="inlineStr">
+      <c r="EY1" t="inlineStr">
         <is>
           <t>study_inc_dur</t>
         </is>
       </c>
-      <c r="EX1" t="inlineStr">
+      <c r="EZ1" t="inlineStr">
         <is>
           <t>study_inc_temp</t>
         </is>
       </c>
-      <c r="EY1" t="inlineStr">
+      <c r="FA1" t="inlineStr">
         <is>
           <t>study_timecourse</t>
         </is>
       </c>
-      <c r="EZ1" t="inlineStr">
+      <c r="FB1" t="inlineStr">
         <is>
           <t>study_tmnt</t>
         </is>
       </c>
-      <c r="FA1" t="inlineStr">
+      <c r="FC1" t="inlineStr">
         <is>
           <t>timepoint</t>
         </is>
       </c>
-      <c r="FB1" t="inlineStr">
+      <c r="FD1" t="inlineStr">
         <is>
           <t>misc_param</t>
         </is>
@@ -1234,13 +1244,13 @@
     <dataValidation sqref="AK2:AK1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"16S rRNA gene,multi-marker approach,other"</formula1>
     </dataValidation>
-    <dataValidation sqref="AX2:AX1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AZ2:AZ1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"marker gene,other,reference based"</formula1>
     </dataValidation>
-    <dataValidation sqref="CK2:CK1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="CM2:CM1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"absent,active,inactive,negative,no,positive,present,yes"</formula1>
     </dataValidation>
-    <dataValidation sqref="EH2:EH1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="EJ2:EJ1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"bottle,cooler,glass vial,plastic vial,vendor supplied container"</formula1>
     </dataValidation>
   </dataValidations>
